--- a/04_DESIGN_TABLES/DesignTable_6410.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6410.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1147,7 +1152,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>1</v>
@@ -1195,12 +1200,17 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1843 = 1.450 (table had 1.32) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX, D@BORE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>6410-06-08-O</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1221,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>0.88</v>
@@ -1259,12 +1269,17 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1844 = 1.100 (table had 0.8) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX; DIFFERS on D@BORE 0.38 vs Brennan B DRILL 0.391 (built to the dimension source, s6)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>6410-08-04-O</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1392,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1385,7 +1400,11 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.16~1.160; C1HEX@HEX=0.88~0.875; D@BORE=0.39~0.391</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1572,7 +1591,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1580,7 +1599,11 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.66~1.660; C1HEX@HEX=1.38~1.375; D@BORE=0.39~0.391</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1706,7 +1729,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -1714,7 +1737,11 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=0.93~0.930; C1HEX@HEX=1~1.000; D@BORE=0.5~0.508</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1965,7 +1992,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -1973,7 +2000,11 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.0 (Lengths to check!E4; website file said 1.000, a filler) = the Air-Way L33 1 already in this row -&gt; no change; OMi and Air-Way agree on the length | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1~1.000; C1HEX@HEX=1.25~1.250; D@BORE=0.38~0.389</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2421,7 +2452,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2429,7 +2460,11 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.0 (Lengths to check!E6; website file said 1.000, a filler) = the Air-Way L33 1 already in this row -&gt; no change; OMi and Air-Way agree on the length | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1~1.000; C1HEX@HEX=1.5~1.500; D@BORE=0.5~0.508</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2494,7 +2529,11 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.12 (Lengths to check!E7; website file said 1.000, a filler) = the Air-Way L33 1.12 already in this row -&gt; no change; OMi and Air-Way agree on the length</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2889,7 +2928,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E10; website file said 1.000, a filler) = the Air-Way L33 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3220,7 +3259,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.26 (Lengths to check!E11; website file said 1.000, a filler) = the Air-Way L33 1.26 already in this row -&gt; no change; OMi and Air-Way agree on the length</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3289,7 +3328,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.27 (Lengths to check!E12; website file said 1.000, a filler) = the Air-Way L33 1.27 already in this row -&gt; no change; OMi and Air-Way agree on the length</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3348,7 +3387,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -3356,7 +3395,11 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.75~1.750; C1HEX@HEX=2.13~2.125; D@BORE=1.31~1.312</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3381,10 +3424,10 @@
         <v>2.75</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>1.544</v>
+        <v>1.53</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>2.5</v>
@@ -3421,7 +3464,7 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP)</t>
+          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.43 (Lengths to check!E15; website file said 1.000, a filler) = the Air-Way L33 1.43 already in this row -&gt; no change; OMi and Air-Way agree on the length | D3@BORE 1.72 -&gt; 1.53: A11 Q-TRANSFER-D3: Air-Way per-size -20 port drill 1.53 instead of the impossible 1.72 (questions_20261008/merged.json orb-port-drill-per-size) | D@BORE 1.544 -&gt; 1.53: A11 Q-BOREWIDE: cap the through bore at the port drill 1.53 (report to OMi)</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3448,7 +3491,7 @@
         <v>2.75</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>1.794</v>
+        <v>1.78</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>1.78</v>
@@ -3488,7 +3531,7 @@
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP)</t>
+          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | D@BORE 1.794 -&gt; 1.78: A11 Q-BOREWIDE: cap the through bore at the port drill 1.78 (report to OMi)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3508,24 +3551,56 @@
           <t>6410-04-02-O</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.075</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>6410-04-02-O</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>7/16-20 (male ORB) x 5/16-24 (female ORB)</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L33 / hex / D from OMi Items (= Brennan TFA p16); male ORB -04 end from the library; female -02 ORB port: no port drill D3 and no measured -02 port geometry yet (own STEP present)</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -3536,6 +3611,11 @@
       <c r="Q48" t="inlineStr">
         <is>
           <t>6410-04-02-O</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3545,24 +3625,56 @@
           <t>6410-16-04-O</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.125</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>6410-16-04-O</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (male ORB) x 7/16-20 (female ORB)</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E5); hex / Side 1 ID OMi website file Items row 1862; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.0 | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -3573,6 +3685,11 @@
       <c r="Q49" t="inlineStr">
         <is>
           <t>6410-16-04-O</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -3582,11 +3699,40 @@
           <t>6410-20-06-O</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.125</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>6410-20-06-O</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (male ORB) x 9/16-18 (female ORB)</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>MISSING</t>
@@ -3594,12 +3740,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E8); hex / Side 1 ID OMi website file Items row 1870; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.509 (Items!S1870) wider than the -06 port drill D3 0.5 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -3610,6 +3756,11 @@
       <c r="Q50" t="inlineStr">
         <is>
           <t>6410-20-06-O</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -3619,11 +3770,40 @@
           <t>6410-20-08-O</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.125</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>6410-20-08-O</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (male ORB) x 3/4-16 (female ORB)</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>MISSING</t>
@@ -3631,12 +3811,12 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E9); hex / Side 1 ID OMi website file Items row 1871; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.689 (Items!S1871) wider than the -08 port drill D3 0.68 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -3647,6 +3827,11 @@
       <c r="Q51" t="inlineStr">
         <is>
           <t>6410-20-08-O</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -3656,11 +3841,37 @@
           <t>6410-32-12-O</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.381</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>6410-32-12-O</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB) x 1 1/16-12 (female ORB)</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>MISSING</t>
@@ -3668,12 +3879,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E13); hex / Side 1 ID OMi website file Items row 1879; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 0.981 (Items!S1879) wider than the -12 port drill D3 0.97 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -3684,6 +3895,11 @@
       <c r="Q52" t="inlineStr">
         <is>
           <t>6410-32-12-O</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -3693,11 +3909,37 @@
           <t>6410-32-16-O</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.381</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>6410-32-16-O</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB) x 1 5/16-12 (female ORB)</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>MISSING</t>
@@ -3705,12 +3947,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E14); hex / Side 1 ID OMi website file Items row 1880; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 1.231 (Items!S1880) wider than the -16 port drill D3 1.22 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -3721,6 +3963,11 @@
       <c r="Q53" t="inlineStr">
         <is>
           <t>6410-32-16-O</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6410.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6410.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.625</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0.17</v>
@@ -679,10 +679,14 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1838 Overall Length = 1.100 (table had 1.25); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1838 Hex Flat = 0.625 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1838 Overall Length = 1.100 (table had 1.25); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1838 Hex Flat = 0.625 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.625) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.1 -&gt; Air-Way 1.25 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.625 -&gt; Air-Way 0.69</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -701,10 +705,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0.17</v>
@@ -744,10 +748,14 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1839 Overall Length = 1.160 (table had 1.2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1839 Hex Flat = 0.812 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1839 Overall Length = 1.160 (table had 1.2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1839 Hex Flat = 0.812 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.812) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.16 -&gt; Air-Way 1.2 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.812 -&gt; Air-Way 0.88</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -958,7 +966,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.6899999999999999</v>
@@ -1001,10 +1009,14 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1841 Overall Length = 1.120 (table had 1.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1841 Overall Length = 1.120 (table had 1.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.12 -&gt; Air-Way 1.03</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1087,7 +1099,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.88</v>
@@ -1130,10 +1142,14 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1842 Overall Length = 1.290 (table had 1.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1842 Overall Length = 1.290 (table had 1.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.16 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.29) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.29 -&gt; Air-Way 1.16</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1152,7 +1168,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>1</v>
@@ -1195,12 +1211,12 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: Air-Way 1.32 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.45) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1843 = 1.450 (table had 1.32) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX, D@BORE</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1843 = 1.450 (table had 1.32) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX, D@BORE | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.45 -&gt; Air-Way 1.32</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1221,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>0.88</v>
@@ -1264,12 +1280,12 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: Air-Way 0.8 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1844 = 1.100 (table had 0.8) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX; DIFFERS on D@BORE 0.38 vs Brennan B DRILL 0.391 (built to the dimension source, s6)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1844 = 1.100 (table had 0.8) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX; DIFFERS on D@BORE 0.38 vs Brennan B DRILL 0.391 (built to the dimension source, s6) | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.1 -&gt; Air-Way 0.8</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1423,7 +1439,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1</v>
@@ -1466,10 +1482,14 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1846 Overall Length = 1.410 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1846 Overall Length = 1.410 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.31 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.31</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1488,7 +1508,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1.13</v>
@@ -1531,10 +1551,14 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1847 Overall Length = 1.480 (table had 1.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1847 Overall Length = 1.480 (table had 1.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.47 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.47</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1760,7 +1784,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>1</v>
@@ -1803,10 +1827,14 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1851 Overall Length = 1.320 (table had 1.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1851 Overall Length = 1.320 (table had 1.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.32 -&gt; Air-Way 1.34</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1889,7 +1917,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1.38</v>
@@ -1932,10 +1960,14 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1853 Overall Length = 1.790 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1853 Overall Length = 1.790 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.79) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.79 -&gt; Air-Way 1.69</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2092,13 +2124,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>1.25</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.609</v>
+        <v>0.68</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>0.68</v>
@@ -2135,10 +2167,14 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1856 Overall Length = 1.480 (table had 1.09); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1856 Side 1 ID = 0.609 (table had 0.68) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1856 Overall Length = 1.480 (table had 1.09); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1856 Side 1 ID = 0.609 (table had 0.68) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.68 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.609) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.09 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.609 -&gt; Air-Way 0.68</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2157,7 +2193,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1.25</v>
@@ -2200,10 +2236,14 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1857 Overall Length = 1.480 (table had 1.56) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1857 Overall Length = 1.480 (table had 1.56) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.56 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.56</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2222,7 +2262,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>1.38</v>
@@ -2265,10 +2305,14 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1858 Overall Length = 1.830 (table had 1.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1858 Overall Length = 1.830 (table had 1.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.83) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.83 -&gt; Air-Way 1.75</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2287,7 +2331,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>1.63</v>
@@ -2330,10 +2374,14 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1859 Overall Length = 1.920 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1859 Overall Length = 1.920 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.92 -&gt; Air-Way 1.88</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2552,7 +2600,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>1.5</v>
@@ -2595,10 +2643,14 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1865 Overall Length = 1.570 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1865 Overall Length = 1.570 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.12 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.57) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.57 -&gt; Air-Way 1.12</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2617,7 +2669,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.5</v>
@@ -2660,10 +2712,14 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1866 Overall Length = 1.710 (table had 1.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1866 Overall Length = 1.710 (table had 1.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.71) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.71 -&gt; Air-Way 1.7</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2682,7 +2738,7 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.63</v>
@@ -2725,12 +2781,12 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1868 Overall Length = 1.81 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1868 Overall Length = 1.81 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.81) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>B(2) printed "1 1/16-12" both passes (a -16 female end is 1 5/16-12; L33/C1/D3 progression supports -16) - as-printed, likely typo</t>
+          <t>B(2) printed "1 1/16-12" both passes (a -16 female end is 1 5/16-12; L33/C1/D3 progression supports -16) - as-printed, likely typo | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.81 -&gt; Air-Way 1.97</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2751,10 +2807,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.84</v>
@@ -2794,10 +2850,14 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1869 Overall Length = 2.140 (table had 2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1869 Hex Flat = 2.125 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1869 Overall Length = 2.140 (table had 2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1869 Hex Flat = 2.125 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 2.14 -&gt; Air-Way 2 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3082,7 +3142,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>2.25</v>
@@ -3125,10 +3185,14 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr"/>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.88</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3485,7 +3549,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>2.75</v>
@@ -3526,12 +3590,12 @@
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1882 Overall Length = 1.440 (table had 1.43); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1882 Side 1 ID = 1.794 (table had 1.78) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1882 Overall Length = 1.440 (table had 1.43); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1882 Side 1 ID = 1.794 (table had 1.78) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.43 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.44) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | D@BORE 1.794 -&gt; 1.78: A11 Q-BOREWIDE: cap the through bore at the port drill 1.78 (report to OMi)</t>
+          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | D@BORE 1.794 -&gt; 1.78: A11 Q-BOREWIDE: cap the through bore at the port drill 1.78 (report to OMi) | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.44 -&gt; Air-Way 1.43</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6410.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6410.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3518,17 +3518,17 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1881 Side 1 ID = 1.544 (table had 1.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1881 Side 1 ID = 1.544 (table had 1.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): unheld - A11 (D3 / D capped at the Air-Way per-size port drill, already applied), A18 (-32 male ORB groove width 0.125 = Brennan 6400-32-32-O STEP, applied by the generator library; ORB_GRVW left empty on purpose) -&gt; ASSUMED (Air-Way single source)</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.43 (Lengths to check!E15; website file said 1.000, a filler) = the Air-Way L33 1.43 already in this row -&gt; no change; OMi and Air-Way agree on the length | D3@BORE 1.72 -&gt; 1.53: A11 Q-TRANSFER-D3: Air-Way per-size -20 port drill 1.53 instead of the impossible 1.72 (questions_20261008/merged.json orb-port-drill-per-size) | D@BORE 1.544 -&gt; 1.53: A11 Q-BOREWIDE: cap the through bore at the port drill 1.53 (report to OMi)</t>
+          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.43 (Lengths to check!E15; website file said 1.000, a filler) = the Air-Way L33 1.43 already in this row -&gt; no change; OMi and Air-Way agree on the length | D3@BORE 1.72 -&gt; 1.53: A11 Q-TRANSFER-D3: Air-Way per-size -20 port drill 1.53 instead of the impossible 1.72 (questions_20261008/merged.json orb-port-drill-per-size) | D@BORE 1.544 -&gt; 1.53: A11 Q-BOREWIDE: cap the through bore at the port drill 1.53 (report to OMi) | 2026-10-20 batch-19 stage A_answered (not shipped): MISSING -&gt; ASSUMED (A11 + A18 answered 2026-10-18; the -32 groove width comes from the end library)</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3585,17 +3585,17 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1882 Overall Length = 1.440 (table had 1.43); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1882 Side 1 ID = 1.794 (table had 1.78) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.43 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.44) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1882 Overall Length = 1.440 (table had 1.43); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1882 Side 1 ID = 1.794 (table had 1.78) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.43 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.44) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): unheld - A11 (D3 / D capped at the Air-Way per-size port drill, already applied), A18 (-32 male ORB groove width 0.125 = Brennan 6400-32-32-O STEP, applied by the generator library; ORB_GRVW left empty on purpose) -&gt; ASSUMED (Air-Way single source)</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | D@BORE 1.794 -&gt; 1.78: A11 Q-BOREWIDE: cap the through bore at the port drill 1.78 (report to OMi) | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.44 -&gt; Air-Way 1.43</t>
+          <t>male-ORB -32 groove width unmeasured (same blocker as 6400/6801 dash-14/32 rows; Brennan STEP) | D@BORE 1.794 -&gt; 1.78: A11 Q-BOREWIDE: cap the through bore at the port drill 1.78 (report to OMi) | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.44 -&gt; Air-Way 1.43 | 2026-10-20 batch-19 stage A_answered (not shipped): MISSING -&gt; ASSUMED (A11 + A18 answered 2026-10-18; the -32 groove width comes from the end library)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3769,6 +3769,9 @@
       <c r="C50" t="n">
         <v>1.875</v>
       </c>
+      <c r="D50" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E50" t="n">
         <v>0.5</v>
       </c>
@@ -3799,17 +3802,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E8); hex / Side 1 ID OMi website file Items row 1870; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E8); hex / Side 1 ID OMi website file Items row 1870; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 0.5 (A11 Q-BOREWIDE; OMi Side 1 ID 0.509 reported to OMi); held reason removed -&gt; ASSUMED (OMi single source)</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.509 (Items!S1870) wider than the -06 port drill D3 0.5 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.509 (Items!S1870) wider than the -06 port drill D3 0.5 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 0.5 (OMi 0.509 wider than the port, report to OMi); MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -3840,6 +3843,9 @@
       <c r="C51" t="n">
         <v>1.875</v>
       </c>
+      <c r="D51" t="n">
+        <v>0.68</v>
+      </c>
       <c r="E51" t="n">
         <v>0.68</v>
       </c>
@@ -3870,17 +3876,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E9); hex / Side 1 ID OMi website file Items row 1871; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E9); hex / Side 1 ID OMi website file Items row 1871; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 0.68 (A11 Q-BOREWIDE; OMi Side 1 ID 0.689 reported to OMi); held reason removed -&gt; ASSUMED (OMi single source)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.689 (Items!S1871) wider than the -08 port drill D3 0.68 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.689 (Items!S1871) wider than the -08 port drill D3 0.68 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 0.68 (OMi 0.689 wider than the port, report to OMi); MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -3911,6 +3917,9 @@
       <c r="C52" t="n">
         <v>2.75</v>
       </c>
+      <c r="D52" t="n">
+        <v>0.97</v>
+      </c>
       <c r="E52" t="n">
         <v>0.97</v>
       </c>
@@ -3938,17 +3947,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E13); hex / Side 1 ID OMi website file Items row 1879; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E13); hex / Side 1 ID OMi website file Items row 1879; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 0.97 (A11 Q-BOREWIDE; OMi Side 1 ID 0.981 reported to OMi); -32 male ORB groove width 0.125 = the Brennan 6400-32-32-O STEP value the generator library applies (A18; ORB_GRVW left empty on purpose); held reason removed -&gt; ASSUMED (OMi single source)</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 0.981 (Items!S1879) wider than the -12 port drill D3 0.97 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 0.981 (Items!S1879) wider than the -12 port drill D3 0.97 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 0.97 (OMi 0.981 wider than the port, report to OMi); A18 groove 0.125 from the library; MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -3979,6 +3988,9 @@
       <c r="C53" t="n">
         <v>2.75</v>
       </c>
+      <c r="D53" t="n">
+        <v>1.22</v>
+      </c>
       <c r="E53" t="n">
         <v>1.22</v>
       </c>
@@ -4006,17 +4018,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E14); hex / Side 1 ID OMi website file Items row 1880; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E14); hex / Side 1 ID OMi website file Items row 1880; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 1.22 (A11 Q-BOREWIDE; OMi Side 1 ID 1.231 reported to OMi); -32 male ORB groove width 0.125 = the Brennan 6400-32-32-O STEP value the generator library applies (A18; ORB_GRVW left empty on purpose); held reason removed -&gt; ASSUMED (OMi single source)</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 1.231 (Items!S1880) wider than the -16 port drill D3 1.22 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 1.231 (Items!S1880) wider than the -16 port drill D3 1.22 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 1.22 (OMi 1.231 wider than the port, report to OMi); A18 groove 0.125 from the library; MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
